--- a/outputs/остатки_себес_плюс_фулфилмент.xlsx
+++ b/outputs/остатки_себес_плюс_фулфилмент.xlsx
@@ -511,14 +511,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ — СЕБЕС + 60 ₽ ФУЛФИЛМЕНТ (нулевые остатки убраны)</t>
+          <t>ОСТАТКИ — СЕБЕС + 60 ₽ ФУЛФИЛМЕНТ (нулевые убраны, цены уточнены)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес = себестоимость по последнему приходу + 60 ₽ фулфилмент. Оставлены только позиции с остатком &gt; 0.</t>
+          <t>Себес = себестоимость + 60 ₽ ФФ. Уточнено вручную: Celimax тонер 828, Round Lab cleanser 512, Dokdo toner 624 (до +ФФ).</t>
         </is>
       </c>
     </row>
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D119" s="7" t="n">
-        <v>523</v>
+        <v>572</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>5499</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>2877022</v>
+        <v>3145428</v>
       </c>
     </row>
     <row r="120">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D123" s="7" t="n">
-        <v>545</v>
+        <v>684</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>802</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>437034</v>
+        <v>548568</v>
       </c>
     </row>
     <row r="124">
@@ -2837,7 +2837,7 @@
         <v>7609</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>4123413</v>
+        <v>4503353</v>
       </c>
     </row>
     <row r="125">
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="D138" s="7" t="n">
-        <v>724</v>
+        <v>888</v>
       </c>
       <c r="E138" s="7" t="n">
         <v>15980</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>11567283</v>
+        <v>14190240</v>
       </c>
     </row>
     <row r="139">
@@ -3309,7 +3309,7 @@
         <v>31554</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>20482834</v>
+        <v>23105791</v>
       </c>
     </row>
     <row r="150">
@@ -3393,13 +3393,13 @@
         <v>107901</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>53937148</v>
+        <v>56940045</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>Остаток 107,901 шт | Денег в товаре (себес+ФФ): 53.94 млн ₽</t>
+          <t>Остаток 107,901 шт | Денег в товаре (себес+ФФ): 56.94 млн ₽</t>
         </is>
       </c>
     </row>
